--- a/Greyform-linux/Python_Application/Pin Allocation BOM for PBU_T1a.xlsx
+++ b/Greyform-linux/Python_Application/Pin Allocation BOM for PBU_T1a.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokZhiZhuan\OneDrive - WINSYS TECHNOLOGY PTE LTD\Documents\GitHub\GreyForm_UI\Greyform\Python_Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE614CA-8FE7-4187-9536-2E81D6DFB99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA36A9CB-9E47-410A-B47E-3A6421EF842C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7215" yWindow="120" windowWidth="23235" windowHeight="15465" xr2:uid="{D0410EE5-F139-4311-88E5-7573157F1556}"/>
+    <workbookView xWindow="1560" yWindow="735" windowWidth="23235" windowHeight="15465" xr2:uid="{D0410EE5-F139-4311-88E5-7573157F1556}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="192">
   <si>
     <t>Stage 1</t>
   </si>
@@ -909,6 +909,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -944,9 +947,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1283,41 +1283,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="30"/>
+      <c r="A1" s="31"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30"/>
-      <c r="B2" s="33" t="s">
+      <c r="A2" s="31"/>
+      <c r="B2" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="30"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="31"/>
     </row>
     <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="30"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1354,11 +1354,11 @@
       <c r="M3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N3" s="30"/>
+      <c r="N3" s="31"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
-      <c r="B4" s="38" t="s">
+      <c r="A4" s="31"/>
+      <c r="B4" s="39" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1">
@@ -1387,11 +1387,11 @@
       <c r="M4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="30"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="28"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="29"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
@@ -1406,11 +1406,11 @@
       <c r="M5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="30"/>
+      <c r="N5" s="31"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
-      <c r="B6" s="28"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="29"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
@@ -1425,11 +1425,11 @@
       <c r="M6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="30"/>
+      <c r="N6" s="31"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="28"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="29"/>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
@@ -1444,11 +1444,11 @@
       <c r="M7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="30"/>
+      <c r="N7" s="31"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="28"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
@@ -1475,11 +1475,11 @@
       <c r="M8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N8" s="30"/>
+      <c r="N8" s="31"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="28"/>
+      <c r="A9" s="31"/>
+      <c r="B9" s="29"/>
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
@@ -1494,11 +1494,11 @@
       <c r="M9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="30"/>
+      <c r="N9" s="31"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="28"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="29"/>
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
@@ -1513,11 +1513,11 @@
       <c r="M10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N10" s="30"/>
+      <c r="N10" s="31"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="28"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="29"/>
       <c r="D11" s="12"/>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
@@ -1532,11 +1532,11 @@
       <c r="M11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N11" s="30"/>
+      <c r="N11" s="31"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
-      <c r="B12" s="28"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="29"/>
       <c r="C12" s="1">
         <v>3</v>
       </c>
@@ -1564,11 +1564,11 @@
         <v>36</v>
       </c>
       <c r="M12" s="23"/>
-      <c r="N12" s="30"/>
+      <c r="N12" s="31"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="30"/>
-      <c r="B13" s="28"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="29"/>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
@@ -1583,11 +1583,11 @@
         <v>36</v>
       </c>
       <c r="M13" s="23"/>
-      <c r="N13" s="30"/>
+      <c r="N13" s="31"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" s="28"/>
+      <c r="A14" s="31"/>
+      <c r="B14" s="29"/>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
@@ -1602,11 +1602,11 @@
         <v>36</v>
       </c>
       <c r="M14" s="23"/>
-      <c r="N14" s="30"/>
+      <c r="N14" s="31"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="28"/>
+      <c r="A15" s="31"/>
+      <c r="B15" s="29"/>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
@@ -1621,11 +1621,11 @@
         <v>36</v>
       </c>
       <c r="M15" s="23"/>
-      <c r="N15" s="30"/>
+      <c r="N15" s="31"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="30"/>
-      <c r="B16" s="28"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="29"/>
       <c r="C16" s="1">
         <v>4</v>
       </c>
@@ -1653,11 +1653,11 @@
         <v>36</v>
       </c>
       <c r="M16" s="23"/>
-      <c r="N16" s="30"/>
+      <c r="N16" s="31"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="30"/>
-      <c r="B17" s="28"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="29"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
@@ -1672,11 +1672,11 @@
         <v>36</v>
       </c>
       <c r="M17" s="23"/>
-      <c r="N17" s="30"/>
+      <c r="N17" s="31"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
-      <c r="B18" s="28"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="29"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
@@ -1691,11 +1691,11 @@
         <v>36</v>
       </c>
       <c r="M18" s="23"/>
-      <c r="N18" s="30"/>
+      <c r="N18" s="31"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="28"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="29"/>
       <c r="D19" s="12"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12"/>
@@ -1710,11 +1710,11 @@
         <v>36</v>
       </c>
       <c r="M19" s="23"/>
-      <c r="N19" s="30"/>
+      <c r="N19" s="31"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
-      <c r="B20" s="28"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="29"/>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12"/>
@@ -1729,11 +1729,11 @@
         <v>36</v>
       </c>
       <c r="M20" s="23"/>
-      <c r="N20" s="30"/>
+      <c r="N20" s="31"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="28"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="29"/>
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12"/>
@@ -1748,11 +1748,11 @@
         <v>36</v>
       </c>
       <c r="M21" s="23"/>
-      <c r="N21" s="30"/>
+      <c r="N21" s="31"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
-      <c r="B22" s="28"/>
+      <c r="A22" s="31"/>
+      <c r="B22" s="29"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
@@ -1767,11 +1767,11 @@
         <v>36</v>
       </c>
       <c r="M22" s="23"/>
-      <c r="N22" s="30"/>
+      <c r="N22" s="31"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="28"/>
+      <c r="A23" s="31"/>
+      <c r="B23" s="29"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
@@ -1786,11 +1786,11 @@
         <v>36</v>
       </c>
       <c r="M23" s="23"/>
-      <c r="N23" s="30"/>
+      <c r="N23" s="31"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="30"/>
-      <c r="B24" s="28"/>
+      <c r="A24" s="31"/>
+      <c r="B24" s="29"/>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -1805,11 +1805,11 @@
         <v>36</v>
       </c>
       <c r="M24" s="23"/>
-      <c r="N24" s="30"/>
+      <c r="N24" s="31"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="30"/>
-      <c r="B25" s="28"/>
+      <c r="A25" s="31"/>
+      <c r="B25" s="29"/>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -1824,11 +1824,11 @@
         <v>36</v>
       </c>
       <c r="M25" s="24"/>
-      <c r="N25" s="30"/>
+      <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="30"/>
-      <c r="B26" s="27" t="s">
+      <c r="A26" s="31"/>
+      <c r="B26" s="28" t="s">
         <v>93</v>
       </c>
       <c r="C26" s="15">
@@ -1858,11 +1858,11 @@
         <v>36</v>
       </c>
       <c r="M26" s="23"/>
-      <c r="N26" s="30"/>
+      <c r="N26" s="31"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
-      <c r="B27" s="28"/>
+      <c r="A27" s="31"/>
+      <c r="B27" s="29"/>
       <c r="F27" s="12"/>
       <c r="H27" s="12"/>
       <c r="J27" s="1" t="s">
@@ -1873,11 +1873,11 @@
         <v>36</v>
       </c>
       <c r="M27" s="23"/>
-      <c r="N27" s="30"/>
+      <c r="N27" s="31"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
-      <c r="B28" s="28"/>
+      <c r="A28" s="31"/>
+      <c r="B28" s="29"/>
       <c r="F28" s="12"/>
       <c r="H28" s="12"/>
       <c r="J28" s="1" t="s">
@@ -1888,11 +1888,11 @@
         <v>36</v>
       </c>
       <c r="M28" s="23"/>
-      <c r="N28" s="30"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="30"/>
-      <c r="B29" s="28"/>
+      <c r="A29" s="31"/>
+      <c r="B29" s="29"/>
       <c r="F29" s="12"/>
       <c r="H29" s="12"/>
       <c r="J29" s="1" t="s">
@@ -1903,11 +1903,11 @@
         <v>36</v>
       </c>
       <c r="M29" s="23"/>
-      <c r="N29" s="30"/>
+      <c r="N29" s="31"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="30"/>
-      <c r="B30" s="28"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="29"/>
       <c r="F30" s="12"/>
       <c r="H30" s="12"/>
       <c r="J30" s="1" t="s">
@@ -1918,11 +1918,11 @@
         <v>36</v>
       </c>
       <c r="M30" s="23"/>
-      <c r="N30" s="30"/>
+      <c r="N30" s="31"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
-      <c r="B31" s="28"/>
+      <c r="A31" s="31"/>
+      <c r="B31" s="29"/>
       <c r="F31" s="12"/>
       <c r="H31" s="12"/>
       <c r="J31" s="1" t="s">
@@ -1933,11 +1933,11 @@
         <v>36</v>
       </c>
       <c r="M31" s="23"/>
-      <c r="N31" s="30"/>
+      <c r="N31" s="31"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="30"/>
-      <c r="B32" s="28"/>
+      <c r="A32" s="31"/>
+      <c r="B32" s="29"/>
       <c r="F32" s="12"/>
       <c r="H32" s="12"/>
       <c r="J32" s="1" t="s">
@@ -1948,11 +1948,11 @@
         <v>36</v>
       </c>
       <c r="M32" s="23"/>
-      <c r="N32" s="30"/>
+      <c r="N32" s="31"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="30"/>
-      <c r="B33" s="29"/>
+      <c r="A33" s="31"/>
+      <c r="B33" s="30"/>
       <c r="F33" s="12"/>
       <c r="H33" s="12"/>
       <c r="J33" s="1" t="s">
@@ -1963,11 +1963,11 @@
         <v>36</v>
       </c>
       <c r="M33" s="23"/>
-      <c r="N33" s="30"/>
+      <c r="N33" s="31"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="30"/>
-      <c r="B34" s="27" t="s">
+      <c r="A34" s="31"/>
+      <c r="B34" s="28" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="15">
@@ -1997,11 +1997,11 @@
       </c>
       <c r="L34" s="17"/>
       <c r="M34" s="18"/>
-      <c r="N34" s="30"/>
+      <c r="N34" s="31"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="30"/>
-      <c r="B35" s="28"/>
+      <c r="A35" s="31"/>
+      <c r="B35" s="29"/>
       <c r="D35" s="1" t="s">
         <v>185</v>
       </c>
@@ -2013,11 +2013,11 @@
       </c>
       <c r="L35" s="19"/>
       <c r="M35" s="7"/>
-      <c r="N35" s="30"/>
+      <c r="N35" s="31"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="30"/>
-      <c r="B36" s="28"/>
+      <c r="A36" s="31"/>
+      <c r="B36" s="29"/>
       <c r="D36" s="1" t="s">
         <v>187</v>
       </c>
@@ -2029,11 +2029,11 @@
       </c>
       <c r="L36" s="19"/>
       <c r="M36" s="7"/>
-      <c r="N36" s="30"/>
+      <c r="N36" s="31"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="30"/>
-      <c r="B37" s="28"/>
+      <c r="A37" s="31"/>
+      <c r="B37" s="29"/>
       <c r="D37" s="1" t="s">
         <v>188</v>
       </c>
@@ -2045,11 +2045,11 @@
       </c>
       <c r="L37" s="19"/>
       <c r="M37" s="7"/>
-      <c r="N37" s="30"/>
+      <c r="N37" s="31"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="30"/>
-      <c r="B38" s="28"/>
+      <c r="A38" s="31"/>
+      <c r="B38" s="29"/>
       <c r="D38" s="1" t="s">
         <v>189</v>
       </c>
@@ -2061,11 +2061,11 @@
       </c>
       <c r="L38" s="19"/>
       <c r="M38" s="7"/>
-      <c r="N38" s="30"/>
+      <c r="N38" s="31"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="30"/>
-      <c r="B39" s="28"/>
+      <c r="A39" s="31"/>
+      <c r="B39" s="29"/>
       <c r="D39" s="1" t="s">
         <v>190</v>
       </c>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="L39" s="19"/>
       <c r="M39" s="7"/>
-      <c r="N39" s="30"/>
+      <c r="N39" s="31"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="30"/>
-      <c r="B40" s="28"/>
-      <c r="D40" s="39" t="s">
+      <c r="A40" s="31"/>
+      <c r="B40" s="29"/>
+      <c r="D40" s="27" t="s">
         <v>191</v>
       </c>
       <c r="J40" s="15" t="s">
@@ -2093,11 +2093,11 @@
       </c>
       <c r="L40" s="19"/>
       <c r="M40" s="7"/>
-      <c r="N40" s="30"/>
+      <c r="N40" s="31"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="30"/>
-      <c r="B41" s="28"/>
+      <c r="A41" s="31"/>
+      <c r="B41" s="29"/>
       <c r="J41" s="15" t="s">
         <v>166</v>
       </c>
@@ -2106,11 +2106,11 @@
       </c>
       <c r="L41" s="19"/>
       <c r="M41" s="7"/>
-      <c r="N41" s="30"/>
+      <c r="N41" s="31"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="30"/>
-      <c r="B42" s="28"/>
+      <c r="A42" s="31"/>
+      <c r="B42" s="29"/>
       <c r="C42" s="1">
         <v>2</v>
       </c>
@@ -2137,11 +2137,11 @@
       </c>
       <c r="L42" s="19"/>
       <c r="M42" s="7"/>
-      <c r="N42" s="30"/>
+      <c r="N42" s="31"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="30"/>
-      <c r="B43" s="28"/>
+      <c r="A43" s="31"/>
+      <c r="B43" s="29"/>
       <c r="J43" s="1" t="s">
         <v>168</v>
       </c>
@@ -2150,11 +2150,11 @@
       </c>
       <c r="L43" s="19"/>
       <c r="M43" s="7"/>
-      <c r="N43" s="30"/>
+      <c r="N43" s="31"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="30"/>
-      <c r="B44" s="28"/>
+      <c r="A44" s="31"/>
+      <c r="B44" s="29"/>
       <c r="J44" s="1" t="s">
         <v>169</v>
       </c>
@@ -2163,11 +2163,11 @@
       </c>
       <c r="L44" s="19"/>
       <c r="M44" s="7"/>
-      <c r="N44" s="30"/>
+      <c r="N44" s="31"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="30"/>
-      <c r="B45" s="28"/>
+      <c r="A45" s="31"/>
+      <c r="B45" s="29"/>
       <c r="J45" s="1" t="s">
         <v>170</v>
       </c>
@@ -2176,11 +2176,11 @@
       </c>
       <c r="L45" s="19"/>
       <c r="M45" s="7"/>
-      <c r="N45" s="30"/>
+      <c r="N45" s="31"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="30"/>
-      <c r="B46" s="28"/>
+      <c r="A46" s="31"/>
+      <c r="B46" s="29"/>
       <c r="C46" s="1">
         <v>3</v>
       </c>
@@ -2210,11 +2210,11 @@
       </c>
       <c r="L46" s="19"/>
       <c r="M46" s="7"/>
-      <c r="N46" s="30"/>
+      <c r="N46" s="31"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="30"/>
-      <c r="B47" s="28"/>
+      <c r="A47" s="31"/>
+      <c r="B47" s="29"/>
       <c r="C47" s="1">
         <v>4</v>
       </c>
@@ -2244,11 +2244,11 @@
       </c>
       <c r="L47" s="19"/>
       <c r="M47" s="7"/>
-      <c r="N47" s="30"/>
+      <c r="N47" s="31"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="30"/>
-      <c r="B48" s="28"/>
+      <c r="A48" s="31"/>
+      <c r="B48" s="29"/>
       <c r="J48" s="1" t="s">
         <v>172</v>
       </c>
@@ -2257,11 +2257,11 @@
       </c>
       <c r="L48" s="19"/>
       <c r="M48" s="7"/>
-      <c r="N48" s="30"/>
+      <c r="N48" s="31"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="30"/>
-      <c r="B49" s="28"/>
+      <c r="A49" s="31"/>
+      <c r="B49" s="29"/>
       <c r="C49" s="1">
         <v>5</v>
       </c>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="L49" s="19"/>
       <c r="M49" s="7"/>
-      <c r="N49" s="30"/>
+      <c r="N49" s="31"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="30"/>
-      <c r="B50" s="28"/>
+      <c r="A50" s="31"/>
+      <c r="B50" s="29"/>
       <c r="J50" s="1" t="s">
         <v>174</v>
       </c>
@@ -2304,11 +2304,11 @@
       </c>
       <c r="L50" s="19"/>
       <c r="M50" s="7"/>
-      <c r="N50" s="30"/>
+      <c r="N50" s="31"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="30"/>
-      <c r="B51" s="28"/>
+      <c r="A51" s="31"/>
+      <c r="B51" s="29"/>
       <c r="C51" s="1">
         <v>6</v>
       </c>
@@ -2338,11 +2338,11 @@
       </c>
       <c r="L51" s="19"/>
       <c r="M51" s="7"/>
-      <c r="N51" s="30"/>
+      <c r="N51" s="31"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="30"/>
-      <c r="B52" s="28"/>
+      <c r="A52" s="31"/>
+      <c r="B52" s="29"/>
       <c r="J52" s="1" t="s">
         <v>176</v>
       </c>
@@ -2351,11 +2351,11 @@
       </c>
       <c r="L52" s="19"/>
       <c r="M52" s="7"/>
-      <c r="N52" s="30"/>
+      <c r="N52" s="31"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="30"/>
-      <c r="B53" s="28"/>
+      <c r="A53" s="31"/>
+      <c r="B53" s="29"/>
       <c r="C53" s="1">
         <v>7</v>
       </c>
@@ -2382,11 +2382,11 @@
       </c>
       <c r="L53" s="19"/>
       <c r="M53" s="7"/>
-      <c r="N53" s="30"/>
+      <c r="N53" s="31"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="30"/>
-      <c r="B54" s="28"/>
+      <c r="A54" s="31"/>
+      <c r="B54" s="29"/>
       <c r="J54" s="1" t="s">
         <v>178</v>
       </c>
@@ -2395,11 +2395,11 @@
       </c>
       <c r="L54" s="19"/>
       <c r="M54" s="7"/>
-      <c r="N54" s="30"/>
+      <c r="N54" s="31"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="30"/>
-      <c r="B55" s="28"/>
+      <c r="A55" s="31"/>
+      <c r="B55" s="29"/>
       <c r="C55" s="1">
         <v>8</v>
       </c>
@@ -2426,11 +2426,11 @@
       </c>
       <c r="L55" s="19"/>
       <c r="M55" s="7"/>
-      <c r="N55" s="30"/>
+      <c r="N55" s="31"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="30"/>
-      <c r="B56" s="28"/>
+      <c r="A56" s="31"/>
+      <c r="B56" s="29"/>
       <c r="J56" s="1" t="s">
         <v>180</v>
       </c>
@@ -2439,11 +2439,11 @@
       </c>
       <c r="L56" s="19"/>
       <c r="M56" s="7"/>
-      <c r="N56" s="30"/>
+      <c r="N56" s="31"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="30"/>
-      <c r="B57" s="28"/>
+      <c r="A57" s="31"/>
+      <c r="B57" s="29"/>
       <c r="C57" s="1">
         <v>9</v>
       </c>
@@ -2471,11 +2471,11 @@
         <v>36</v>
       </c>
       <c r="M57" s="7"/>
-      <c r="N57" s="30"/>
+      <c r="N57" s="31"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="30"/>
-      <c r="B58" s="28"/>
+      <c r="A58" s="31"/>
+      <c r="B58" s="29"/>
       <c r="J58" s="1" t="s">
         <v>182</v>
       </c>
@@ -2484,11 +2484,11 @@
         <v>36</v>
       </c>
       <c r="M58" s="7"/>
-      <c r="N58" s="30"/>
+      <c r="N58" s="31"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="30"/>
-      <c r="B59" s="29"/>
+      <c r="A59" s="31"/>
+      <c r="B59" s="30"/>
       <c r="J59" s="1" t="s">
         <v>183</v>
       </c>
@@ -2497,11 +2497,11 @@
         <v>36</v>
       </c>
       <c r="M59" s="7"/>
-      <c r="N59" s="30"/>
+      <c r="N59" s="31"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="30"/>
-      <c r="B60" s="27" t="s">
+      <c r="A60" s="31"/>
+      <c r="B60" s="28" t="s">
         <v>5</v>
       </c>
       <c r="C60" s="15">
@@ -2526,14 +2526,16 @@
       <c r="J60" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="K60" s="20"/>
+      <c r="K60" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="L60" s="17"/>
       <c r="M60" s="18"/>
-      <c r="N60" s="30"/>
+      <c r="N60" s="31"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="30"/>
-      <c r="B61" s="28"/>
+      <c r="A61" s="31"/>
+      <c r="B61" s="29"/>
       <c r="C61" s="1">
         <v>2</v>
       </c>
@@ -2560,11 +2562,11 @@
       <c r="M61" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N61" s="30"/>
+      <c r="N61" s="31"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="30"/>
-      <c r="B62" s="28"/>
+      <c r="A62" s="31"/>
+      <c r="B62" s="29"/>
       <c r="D62" s="1" t="s">
         <v>186</v>
       </c>
@@ -2576,11 +2578,11 @@
       <c r="M62" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N62" s="30"/>
+      <c r="N62" s="31"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="30"/>
-      <c r="B63" s="28"/>
+      <c r="A63" s="31"/>
+      <c r="B63" s="29"/>
       <c r="C63" s="1">
         <v>3</v>
       </c>
@@ -2608,11 +2610,11 @@
         <v>36</v>
       </c>
       <c r="M63" s="23"/>
-      <c r="N63" s="30"/>
+      <c r="N63" s="31"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="30"/>
-      <c r="B64" s="28"/>
+      <c r="A64" s="31"/>
+      <c r="B64" s="29"/>
       <c r="J64" s="1" t="s">
         <v>104</v>
       </c>
@@ -2621,11 +2623,11 @@
         <v>36</v>
       </c>
       <c r="M64" s="23"/>
-      <c r="N64" s="30"/>
+      <c r="N64" s="31"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="30"/>
-      <c r="B65" s="28"/>
+      <c r="A65" s="31"/>
+      <c r="B65" s="29"/>
       <c r="J65" s="1" t="s">
         <v>105</v>
       </c>
@@ -2634,11 +2636,11 @@
         <v>36</v>
       </c>
       <c r="M65" s="23"/>
-      <c r="N65" s="30"/>
+      <c r="N65" s="31"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="30"/>
-      <c r="B66" s="28"/>
+      <c r="A66" s="31"/>
+      <c r="B66" s="29"/>
       <c r="J66" s="1" t="s">
         <v>106</v>
       </c>
@@ -2647,11 +2649,11 @@
         <v>36</v>
       </c>
       <c r="M66" s="23"/>
-      <c r="N66" s="30"/>
+      <c r="N66" s="31"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="30"/>
-      <c r="B67" s="29"/>
+      <c r="A67" s="31"/>
+      <c r="B67" s="30"/>
       <c r="J67" s="1" t="s">
         <v>107</v>
       </c>
@@ -2660,11 +2662,11 @@
         <v>36</v>
       </c>
       <c r="M67" s="23"/>
-      <c r="N67" s="30"/>
+      <c r="N67" s="31"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="30"/>
-      <c r="B68" s="27" t="s">
+      <c r="A68" s="31"/>
+      <c r="B68" s="28" t="s">
         <v>4</v>
       </c>
       <c r="C68" s="15">
@@ -2694,11 +2696,11 @@
       <c r="M68" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="N68" s="30"/>
+      <c r="N68" s="31"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="30"/>
-      <c r="B69" s="28"/>
+      <c r="A69" s="31"/>
+      <c r="B69" s="29"/>
       <c r="J69" s="1" t="s">
         <v>144</v>
       </c>
@@ -2707,11 +2709,11 @@
       <c r="M69" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N69" s="30"/>
+      <c r="N69" s="31"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="30"/>
-      <c r="B70" s="28"/>
+      <c r="A70" s="31"/>
+      <c r="B70" s="29"/>
       <c r="J70" s="1" t="s">
         <v>145</v>
       </c>
@@ -2720,11 +2722,11 @@
       <c r="M70" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N70" s="30"/>
+      <c r="N70" s="31"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="30"/>
-      <c r="B71" s="28"/>
+      <c r="A71" s="31"/>
+      <c r="B71" s="29"/>
       <c r="J71" s="1" t="s">
         <v>146</v>
       </c>
@@ -2733,10 +2735,10 @@
       <c r="M71" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N71" s="30"/>
+      <c r="N71" s="31"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B72" s="28"/>
+      <c r="B72" s="29"/>
       <c r="C72" s="1">
         <v>2</v>
       </c>
@@ -2765,7 +2767,7 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B73" s="28"/>
+      <c r="B73" s="29"/>
       <c r="J73" s="1" t="s">
         <v>149</v>
       </c>
@@ -2776,7 +2778,7 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B74" s="28"/>
+      <c r="B74" s="29"/>
       <c r="J74" s="1" t="s">
         <v>150</v>
       </c>
@@ -2787,7 +2789,7 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B75" s="28"/>
+      <c r="B75" s="29"/>
       <c r="J75" s="1" t="s">
         <v>151</v>
       </c>
@@ -2798,7 +2800,7 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B76" s="28"/>
+      <c r="B76" s="29"/>
       <c r="C76" s="1">
         <v>3</v>
       </c>
@@ -2827,7 +2829,7 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B77" s="28"/>
+      <c r="B77" s="29"/>
       <c r="J77" s="1" t="s">
         <v>153</v>
       </c>
@@ -2838,7 +2840,7 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B78" s="28"/>
+      <c r="B78" s="29"/>
       <c r="J78" s="1" t="s">
         <v>154</v>
       </c>
@@ -2849,7 +2851,7 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B79" s="28"/>
+      <c r="B79" s="29"/>
       <c r="J79" s="1" t="s">
         <v>155</v>
       </c>
@@ -2860,7 +2862,7 @@
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B80" s="28"/>
+      <c r="B80" s="29"/>
       <c r="C80" s="1">
         <v>4</v>
       </c>
@@ -2892,7 +2894,7 @@
       <c r="M80" s="7"/>
     </row>
     <row r="81" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B81" s="28"/>
+      <c r="B81" s="29"/>
       <c r="J81" s="1" t="s">
         <v>59</v>
       </c>
@@ -2903,7 +2905,7 @@
       <c r="M81" s="7"/>
     </row>
     <row r="82" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B82" s="28"/>
+      <c r="B82" s="29"/>
       <c r="C82" s="1">
         <v>5</v>
       </c>
@@ -2932,7 +2934,7 @@
       <c r="M82" s="7"/>
     </row>
     <row r="83" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B83" s="28"/>
+      <c r="B83" s="29"/>
       <c r="C83" s="1">
         <v>6</v>
       </c>
@@ -2964,7 +2966,7 @@
       <c r="M83" s="7"/>
     </row>
     <row r="84" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B84" s="28"/>
+      <c r="B84" s="29"/>
       <c r="C84" s="1">
         <v>7</v>
       </c>
@@ -2996,7 +2998,7 @@
       <c r="M84" s="7"/>
     </row>
     <row r="85" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B85" s="28"/>
+      <c r="B85" s="29"/>
       <c r="C85" s="1">
         <v>8</v>
       </c>
@@ -3026,7 +3028,7 @@
       <c r="M85" s="7"/>
     </row>
     <row r="86" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B86" s="28"/>
+      <c r="B86" s="29"/>
       <c r="J86" s="1" t="s">
         <v>158</v>
       </c>
@@ -3037,7 +3039,7 @@
       <c r="M86" s="7"/>
     </row>
     <row r="87" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B87" s="28"/>
+      <c r="B87" s="29"/>
       <c r="J87" s="1" t="s">
         <v>159</v>
       </c>
@@ -3048,7 +3050,7 @@
       <c r="M87" s="7"/>
     </row>
     <row r="88" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B88" s="28"/>
+      <c r="B88" s="29"/>
       <c r="J88" s="1" t="s">
         <v>160</v>
       </c>
@@ -3059,7 +3061,7 @@
       <c r="M88" s="7"/>
     </row>
     <row r="89" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B89" s="27" t="s">
+      <c r="B89" s="28" t="s">
         <v>10</v>
       </c>
       <c r="C89" s="15">
@@ -3091,7 +3093,7 @@
       <c r="M89" s="18"/>
     </row>
     <row r="90" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B90" s="28"/>
+      <c r="B90" s="29"/>
       <c r="C90" s="1">
         <v>2</v>
       </c>
@@ -3121,7 +3123,7 @@
       <c r="M90" s="7"/>
     </row>
     <row r="91" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B91" s="28"/>
+      <c r="B91" s="29"/>
       <c r="J91" s="1" t="s">
         <v>109</v>
       </c>
@@ -3132,7 +3134,7 @@
       <c r="M91" s="7"/>
     </row>
     <row r="92" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B92" s="28"/>
+      <c r="B92" s="29"/>
       <c r="J92" s="1" t="s">
         <v>110</v>
       </c>
@@ -3143,7 +3145,7 @@
       <c r="M92" s="7"/>
     </row>
     <row r="93" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B93" s="28"/>
+      <c r="B93" s="29"/>
       <c r="J93" s="1" t="s">
         <v>111</v>
       </c>
@@ -3154,7 +3156,7 @@
       <c r="M93" s="7"/>
     </row>
     <row r="94" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B94" s="28"/>
+      <c r="B94" s="29"/>
       <c r="J94" s="1" t="s">
         <v>112</v>
       </c>
@@ -3165,7 +3167,7 @@
       <c r="M94" s="7"/>
     </row>
     <row r="95" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B95" s="29"/>
+      <c r="B95" s="30"/>
       <c r="J95" s="1" t="s">
         <v>113</v>
       </c>
@@ -3175,7 +3177,7 @@
       <c r="M95" s="22"/>
     </row>
     <row r="96" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B96" s="27" t="s">
+      <c r="B96" s="28" t="s">
         <v>9</v>
       </c>
       <c r="C96" s="15">
@@ -3207,7 +3209,7 @@
       <c r="M96" s="18"/>
     </row>
     <row r="97" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B97" s="28"/>
+      <c r="B97" s="29"/>
       <c r="J97" s="1" t="s">
         <v>65</v>
       </c>
@@ -3218,7 +3220,7 @@
       <c r="M97" s="7"/>
     </row>
     <row r="98" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B98" s="28"/>
+      <c r="B98" s="29"/>
       <c r="J98" s="1" t="s">
         <v>66</v>
       </c>
@@ -3229,7 +3231,7 @@
       <c r="M98" s="7"/>
     </row>
     <row r="99" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B99" s="28"/>
+      <c r="B99" s="29"/>
       <c r="J99" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,7 +3242,7 @@
       <c r="M99" s="7"/>
     </row>
     <row r="100" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B100" s="28"/>
+      <c r="B100" s="29"/>
       <c r="C100" s="1">
         <v>2</v>
       </c>
@@ -3267,7 +3269,7 @@
       <c r="M100" s="7"/>
     </row>
     <row r="101" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B101" s="28"/>
+      <c r="B101" s="29"/>
       <c r="C101" s="1">
         <v>3</v>
       </c>
@@ -3299,7 +3301,7 @@
       <c r="M101" s="7"/>
     </row>
     <row r="102" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B102" s="28"/>
+      <c r="B102" s="29"/>
       <c r="J102" s="1" t="s">
         <v>69</v>
       </c>
@@ -3310,7 +3312,7 @@
       <c r="M102" s="7"/>
     </row>
     <row r="103" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B103" s="28"/>
+      <c r="B103" s="29"/>
       <c r="J103" s="1" t="s">
         <v>70</v>
       </c>
@@ -3321,7 +3323,7 @@
       <c r="M103" s="7"/>
     </row>
     <row r="104" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B104" s="28"/>
+      <c r="B104" s="29"/>
       <c r="J104" s="1" t="s">
         <v>71</v>
       </c>
@@ -3332,7 +3334,7 @@
       <c r="M104" s="7"/>
     </row>
     <row r="105" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B105" s="28"/>
+      <c r="B105" s="29"/>
       <c r="C105" s="1">
         <v>4</v>
       </c>
@@ -3364,7 +3366,7 @@
       <c r="M105" s="7"/>
     </row>
     <row r="106" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B106" s="28"/>
+      <c r="B106" s="29"/>
       <c r="J106" s="1" t="s">
         <v>73</v>
       </c>
@@ -3375,7 +3377,7 @@
       <c r="M106" s="7"/>
     </row>
     <row r="107" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B107" s="28"/>
+      <c r="B107" s="29"/>
       <c r="J107" s="1" t="s">
         <v>74</v>
       </c>
@@ -3386,7 +3388,7 @@
       <c r="M107" s="7"/>
     </row>
     <row r="108" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B108" s="28"/>
+      <c r="B108" s="29"/>
       <c r="J108" s="1" t="s">
         <v>75</v>
       </c>
@@ -3397,7 +3399,7 @@
       <c r="M108" s="7"/>
     </row>
     <row r="109" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B109" s="28"/>
+      <c r="B109" s="29"/>
       <c r="C109" s="1">
         <v>5</v>
       </c>
@@ -3427,7 +3429,7 @@
       <c r="M109" s="7"/>
     </row>
     <row r="110" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B110" s="28"/>
+      <c r="B110" s="29"/>
       <c r="J110" s="1" t="s">
         <v>115</v>
       </c>
@@ -3438,7 +3440,7 @@
       <c r="M110" s="7"/>
     </row>
     <row r="111" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B111" s="28"/>
+      <c r="B111" s="29"/>
       <c r="J111" s="1" t="s">
         <v>116</v>
       </c>
@@ -3449,7 +3451,7 @@
       <c r="M111" s="7"/>
     </row>
     <row r="112" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B112" s="28"/>
+      <c r="B112" s="29"/>
       <c r="J112" s="1" t="s">
         <v>117</v>
       </c>
@@ -3460,7 +3462,7 @@
       <c r="M112" s="7"/>
     </row>
     <row r="113" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B113" s="28"/>
+      <c r="B113" s="29"/>
       <c r="J113" s="1" t="s">
         <v>118</v>
       </c>
@@ -3471,7 +3473,7 @@
       <c r="M113" s="7"/>
     </row>
     <row r="114" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B114" s="28"/>
+      <c r="B114" s="29"/>
       <c r="J114" s="1" t="s">
         <v>119</v>
       </c>
@@ -3482,7 +3484,7 @@
       <c r="M114" s="7"/>
     </row>
     <row r="115" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B115" s="28"/>
+      <c r="B115" s="29"/>
       <c r="J115" s="1" t="s">
         <v>120</v>
       </c>
@@ -3493,7 +3495,7 @@
       <c r="M115" s="7"/>
     </row>
     <row r="116" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B116" s="28"/>
+      <c r="B116" s="29"/>
       <c r="J116" s="1" t="s">
         <v>121</v>
       </c>
@@ -3504,7 +3506,7 @@
       <c r="M116" s="7"/>
     </row>
     <row r="117" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B117" s="28"/>
+      <c r="B117" s="29"/>
       <c r="J117" s="1" t="s">
         <v>122</v>
       </c>
@@ -3515,7 +3517,7 @@
       <c r="M117" s="7"/>
     </row>
     <row r="118" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B118" s="28"/>
+      <c r="B118" s="29"/>
       <c r="J118" s="1" t="s">
         <v>123</v>
       </c>
@@ -3526,7 +3528,7 @@
       <c r="M118" s="7"/>
     </row>
     <row r="119" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B119" s="28"/>
+      <c r="B119" s="29"/>
       <c r="J119" s="1" t="s">
         <v>124</v>
       </c>
@@ -3537,7 +3539,7 @@
       <c r="M119" s="7"/>
     </row>
     <row r="120" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B120" s="28"/>
+      <c r="B120" s="29"/>
       <c r="J120" s="1" t="s">
         <v>125</v>
       </c>
@@ -3548,7 +3550,7 @@
       <c r="M120" s="7"/>
     </row>
     <row r="121" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B121" s="28"/>
+      <c r="B121" s="29"/>
       <c r="J121" s="1" t="s">
         <v>126</v>
       </c>
@@ -3559,7 +3561,7 @@
       <c r="M121" s="7"/>
     </row>
     <row r="122" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B122" s="28"/>
+      <c r="B122" s="29"/>
       <c r="J122" s="1" t="s">
         <v>127</v>
       </c>
@@ -3570,7 +3572,7 @@
       <c r="M122" s="7"/>
     </row>
     <row r="123" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B123" s="28"/>
+      <c r="B123" s="29"/>
       <c r="C123" s="1">
         <v>6</v>
       </c>
@@ -3600,7 +3602,7 @@
       <c r="M123" s="7"/>
     </row>
     <row r="124" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B124" s="28"/>
+      <c r="B124" s="29"/>
       <c r="J124" s="1" t="s">
         <v>129</v>
       </c>
@@ -3611,7 +3613,7 @@
       <c r="M124" s="7"/>
     </row>
     <row r="125" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B125" s="28"/>
+      <c r="B125" s="29"/>
       <c r="C125" s="1">
         <v>7</v>
       </c>
@@ -3641,7 +3643,7 @@
       <c r="M125" s="7"/>
     </row>
     <row r="126" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B126" s="28"/>
+      <c r="B126" s="29"/>
       <c r="J126" s="1" t="s">
         <v>131</v>
       </c>
@@ -3652,7 +3654,7 @@
       <c r="M126" s="7"/>
     </row>
     <row r="127" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B127" s="28"/>
+      <c r="B127" s="29"/>
       <c r="J127" s="1" t="s">
         <v>132</v>
       </c>
@@ -3663,7 +3665,7 @@
       <c r="M127" s="7"/>
     </row>
     <row r="128" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B128" s="28"/>
+      <c r="B128" s="29"/>
       <c r="J128" s="1" t="s">
         <v>133</v>
       </c>
@@ -3674,7 +3676,7 @@
       <c r="M128" s="7"/>
     </row>
     <row r="129" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B129" s="28"/>
+      <c r="B129" s="29"/>
       <c r="J129" s="1" t="s">
         <v>134</v>
       </c>
@@ -3685,7 +3687,7 @@
       <c r="M129" s="7"/>
     </row>
     <row r="130" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B130" s="29"/>
+      <c r="B130" s="30"/>
       <c r="J130" s="1" t="s">
         <v>135</v>
       </c>
@@ -3737,30 +3739,30 @@
         <f>SUM(H4:H131)</f>
         <v>126</v>
       </c>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-      <c r="G132" s="36"/>
-      <c r="H132" s="36"/>
-      <c r="I132" s="36"/>
-      <c r="J132" s="36"/>
-      <c r="K132" s="36"/>
-      <c r="L132" s="36"/>
-      <c r="M132" s="37"/>
+      <c r="D132" s="37"/>
+      <c r="E132" s="37"/>
+      <c r="F132" s="37"/>
+      <c r="G132" s="37"/>
+      <c r="H132" s="37"/>
+      <c r="I132" s="37"/>
+      <c r="J132" s="37"/>
+      <c r="K132" s="37"/>
+      <c r="L132" s="37"/>
+      <c r="M132" s="38"/>
     </row>
     <row r="133" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B133" s="30"/>
-      <c r="C133" s="30"/>
-      <c r="D133" s="31"/>
-      <c r="E133" s="31"/>
-      <c r="F133" s="31"/>
-      <c r="G133" s="31"/>
-      <c r="H133" s="31"/>
-      <c r="I133" s="31"/>
-      <c r="J133" s="31"/>
-      <c r="K133" s="31"/>
-      <c r="L133" s="31"/>
-      <c r="M133" s="31"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="31"/>
+      <c r="D133" s="32"/>
+      <c r="E133" s="32"/>
+      <c r="F133" s="32"/>
+      <c r="G133" s="32"/>
+      <c r="H133" s="32"/>
+      <c r="I133" s="32"/>
+      <c r="J133" s="32"/>
+      <c r="K133" s="32"/>
+      <c r="L133" s="32"/>
+      <c r="M133" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="13">
